--- a/outputs/test_takeoff_output.xlsx
+++ b/outputs/test_takeoff_output.xlsx
@@ -61,8 +61,8 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00C0392B"/>
-      <sz val="10"/>
+      <color rgb="00E67E22"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -98,8 +98,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDECEF"/>
-        <bgColor rgb="00FDECEF"/>
+        <fgColor rgb="00FDF7F2"/>
+        <bgColor rgb="00FDF7F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -156,7 +156,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -631,7 +631,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>69.3%</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>REJECTED (Low Quality)</t>
+          <t>REVIEW REQUIRED</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -684,364 +684,160 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Dimension mismatch for W1 (STUDY): Plans 2136H×820W vs NatHERS 2057H×1210W.</t>
+          <t>Dimension mismatch for 1118 (Bedroom 3): Plans 1100H×1800W vs NatHERS 1100H×1810W.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Type Mismatch</t>
+          <t>Dimension Mismatch</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Type mismatch for W1 (STUDY): Plans 'sliding door' vs NatHERS 'Awning'.</t>
+          <t>Dimension mismatch for 1006 (ens): Plans 1000H×600W vs NatHERS 1800H×600W.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Glazing Mismatch</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Glazing mismatch for W1 (STUDY): Plans 'Standard' vs NatHERS '150 Series Thermal Star Aluminium Awning Window - With In-Line Reveal - Single Glazed'.</t>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Missing in Plans</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Low Confidence</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>W1 (STUDY): Low confidence (55%) — verify specs manually.</t>
+          <t>Missing in Plans</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>1117 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Dimension Mismatch</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for W2 (BED 1): Plans 1806H×1118W vs NatHERS 1800H×2650W.</t>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Missing in Plans</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>Glazing Mismatch</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Glazing mismatch for W2 (BED 1): Plans 'Standard' vs NatHERS '150 Series Thermal Star Aluminium Awning Window - With In-Line Reveal - Single Glazed'.</t>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Missing in Plans</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>1818 (Bedroom 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Dimension Mismatch</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for W3 (ENS): Plans 1806H×1115W vs NatHERS 1800H×610W.</t>
+          <t>1124</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Missing in Plans</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>1124 (Kitchen/Living) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>Glazing Mismatch</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Glazing mismatch for W3 (ENS): Plans 'Standard' vs NatHERS '150 Series Thermal Star Aluminium Awning Window - With In-Line Reveal - Single Glazed'.</t>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Missing in Plans</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>D1 (LDRY) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>Dimension Mismatch</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for W4 (KITCHEN/FAMILY/DINING): Plans 1806H×1806W vs NatHERS 1800H×3010W.</t>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Missing in Plans</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>D2 (ENTRY) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>BASIX Glazing Total</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Glazing Mismatch</t>
+          <t>BASIX Area Mismatch</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Glazing mismatch for W4 (KITCHEN/FAMILY/DINING): Plans 'Standard' vs NatHERS '150 Series Thermal Star Aluminium Awning Window - With In-Line Reveal - Single Glazed'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Dimension Mismatch</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for W5 (LOUNGE): Plans 1806H×1806W vs NatHERS 1800H×2400W.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>Glazing Mismatch</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>Glazing mismatch for W5 (LOUNGE): Plans 'Standard' vs NatHERS '150 Series Thermal Star Aluminium Awning Window - With In-Line Reveal - Single Glazed'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Dimension Mismatch</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for D1 (L'DRY): Plans 2136H×820W vs NatHERS 2100H×1450W.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>Glazing Mismatch</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>Glazing mismatch for D1 (L'DRY): Plans 'Standard' vs NatHERS '100 SERIES - ALUMINIUM SLIDING DOOR'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>W8 (BATH) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>W10 (BED 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>W11 (BED 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>W9 (BED 3) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>W7 (BED 4) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>D2 (KITCHEN/FAMILY/DINING) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>W6 (LOUNGE) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>BASIX Glazing Total</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>BASIX Area Mismatch</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>Extracted plan glazing area (29.85 m²) differs from BASIX certificate total (36.90 m²) by 19.1%. The BASIX/NatHERS certificate value (36.90 m²) is the verified anchor. Review the plan extraction for under-counting — possible phantom openings, excluded door types, or scanned-page misreads.</t>
+          <t>Extracted plan glazing area (28.90 m²) differs from BASIX certificate total (36.90 m²) by 21.7%. The BASIX/NatHERS certificate value (36.90 m²) is the verified anchor. Review the plan extraction for under-counting — possible phantom openings, excluded door types, or scanned-page misreads.</t>
         </is>
       </c>
     </row>
@@ -1056,16 +852,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="89" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -1145,40 +941,40 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>STUDY</t>
+          <t>Kitchen/Living</t>
         </is>
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>2136ALSD</t>
         </is>
       </c>
       <c r="C3" s="16" t="n">
-        <v>2136</v>
+        <v>2100</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>820</v>
+        <v>3600</v>
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>Awning</t>
+          <t>sliding</t>
         </is>
       </c>
       <c r="F3" s="15" t="inlineStr">
         <is>
-          <t>ENE</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>150 Series Thermal Star Aluminium Awning Window - With In-Line Reveal - Single Glazed</t>
+          <t>Aluminium B SG High Solar Gain Low-E</t>
         </is>
       </c>
       <c r="H3" s="15" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="I3" s="15" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="J3" s="14" t="inlineStr">
         <is>
@@ -1190,47 +986,47 @@
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>Plans p.4 / NatHERS p.5, p.6</t>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>BED 1</t>
+          <t>WIR</t>
         </is>
       </c>
       <c r="B4" s="18" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="C4" s="19" t="n">
-        <v>1806</v>
+        <v>1800</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>1118</v>
+        <v>600</v>
       </c>
       <c r="E4" s="17" t="inlineStr">
         <is>
-          <t>Awning</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
         <is>
-          <t>SSE</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>150 Series Thermal Star Aluminium Awning Window - With In-Line Reveal - Single Glazed</t>
+          <t>Aluminium B SG Clear</t>
         </is>
       </c>
       <c r="H4" s="18" t="n">
-        <v>4.1</v>
+        <v>6.7</v>
       </c>
       <c r="I4" s="18" t="n">
-        <v>0.53</v>
+        <v>0.7</v>
       </c>
       <c r="J4" s="17" t="inlineStr">
         <is>
@@ -1242,47 +1038,47 @@
       </c>
       <c r="L4" s="17" t="inlineStr">
         <is>
-          <t>Plans p.4 / NatHERS p.5, p.6</t>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>ENS</t>
+          <t>Bedroom 3</t>
         </is>
       </c>
       <c r="B5" s="18" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="C5" s="19" t="n">
-        <v>1806</v>
+        <v>1100</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>1115</v>
+        <v>1810</v>
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>Awning</t>
+          <t>sliding</t>
         </is>
       </c>
       <c r="F5" s="18" t="inlineStr">
         <is>
-          <t>SSE</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
-          <t>150 Series Thermal Star Aluminium Awning Window - With In-Line Reveal - Single Glazed</t>
+          <t>Aluminium B SG Clear</t>
         </is>
       </c>
       <c r="H5" s="18" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="I5" s="18" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
@@ -1294,47 +1090,47 @@
       </c>
       <c r="L5" s="17" t="inlineStr">
         <is>
-          <t>Plans p.4 / NatHERS p.5, p.6</t>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>KITCHEN/FAMILY/DINING</t>
+          <t>BATH</t>
         </is>
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="C6" s="19" t="n">
-        <v>1806</v>
+        <v>1100</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>1806</v>
+        <v>1500</v>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>Awning</t>
+          <t>sliding</t>
         </is>
       </c>
       <c r="F6" s="18" t="inlineStr">
         <is>
-          <t>WSW</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>150 Series Thermal Star Aluminium Awning Window - With In-Line Reveal - Single Glazed</t>
+          <t>Aluminium B SG Clear</t>
         </is>
       </c>
       <c r="H6" s="18" t="n">
-        <v>4.1</v>
+        <v>6.7</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>0.53</v>
+        <v>0.7</v>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
@@ -1346,47 +1142,47 @@
       </c>
       <c r="L6" s="17" t="inlineStr">
         <is>
-          <t>Plans p.4 / NatHERS p.5, p.6</t>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>LOUNGE</t>
+          <t>ens</t>
         </is>
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="C7" s="19" t="n">
-        <v>1806</v>
+        <v>1800</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>1806</v>
+        <v>600</v>
       </c>
       <c r="E7" s="17" t="inlineStr">
         <is>
-          <t>Awning</t>
+          <t>awning</t>
         </is>
       </c>
       <c r="F7" s="18" t="inlineStr">
         <is>
-          <t>WSW</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t>150 Series Thermal Star Aluminium Awning Window - With In-Line Reveal - Single Glazed</t>
+          <t>Aluminium A SG Clear</t>
         </is>
       </c>
       <c r="H7" s="18" t="n">
-        <v>4.1</v>
+        <v>6.7</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
@@ -1398,99 +1194,99 @@
       </c>
       <c r="L7" s="17" t="inlineStr">
         <is>
-          <t>Plans p.4 / NatHERS p.5, p.6</t>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>L'DRY</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="n">
-        <v>2136</v>
-      </c>
-      <c r="D8" s="22" t="n">
-        <v>820</v>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>Sliding Door</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>WSW</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
-        <is>
-          <t>100 SERIES - ALUMINIUM SLIDING DOOR</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="I8" s="21" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Kitchen/Living</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>awning</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium A SG Clear</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K8" s="22" t="n">
+      <c r="K8" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L8" s="20" t="inlineStr">
-        <is>
-          <t>Plans p.4 / NatHERS p.5, p.6</t>
+      <c r="L8" s="17" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>BATH</t>
+          <t>Kitchen/Living</t>
         </is>
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="C9" s="19" t="n">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>1450</v>
+        <v>600</v>
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>Awning</t>
+          <t>awning</t>
         </is>
       </c>
       <c r="F9" s="18" t="inlineStr">
         <is>
-          <t>NNW</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>150 Series Thermal Star Aluminium Awning Window - With In-Line Reveal - Single Glazed</t>
+          <t>Aluminium A SG Clear</t>
         </is>
       </c>
       <c r="H9" s="18" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
@@ -1502,47 +1298,47 @@
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
-          <t>NatHERS p.5, p.6</t>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>BED 2</t>
+          <t>Kitchen/Living</t>
         </is>
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="C10" s="19" t="n">
-        <v>2057</v>
+        <v>1800</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>1210</v>
+        <v>600</v>
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>Awning</t>
+          <t>awning</t>
         </is>
       </c>
       <c r="F10" s="18" t="inlineStr">
         <is>
-          <t>ENE</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>150 Series Thermal Star Aluminium Awning Window - With In-Line Reveal - Single Glazed</t>
+          <t>Aluminium A SG Clear</t>
         </is>
       </c>
       <c r="H10" s="18" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="I10" s="18" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
@@ -1554,47 +1350,47 @@
       </c>
       <c r="L10" s="17" t="inlineStr">
         <is>
-          <t>NatHERS p.5, p.6</t>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>BED 2</t>
+          <t>Bedroom 1</t>
         </is>
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="C11" s="19" t="n">
-        <v>2057</v>
+        <v>1100</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>1210</v>
+        <v>500</v>
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>Awning</t>
+          <t>awning</t>
         </is>
       </c>
       <c r="F11" s="18" t="inlineStr">
         <is>
-          <t>ENE</t>
+          <t>SW</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>150 Series Thermal Star Aluminium Awning Window - With In-Line Reveal - Single Glazed</t>
+          <t>Aluminium A SG Clear</t>
         </is>
       </c>
       <c r="H11" s="18" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
@@ -1606,47 +1402,47 @@
       </c>
       <c r="L11" s="17" t="inlineStr">
         <is>
-          <t>NatHERS p.5, p.6</t>
+          <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>BED 3</t>
+          <t>Bedroom 1</t>
         </is>
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="C12" s="19" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>1450</v>
+        <v>1700</v>
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t>Awning</t>
+          <t>double_hung</t>
         </is>
       </c>
       <c r="F12" s="18" t="inlineStr">
         <is>
-          <t>NNW</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>150 Series Thermal Star Aluminium Awning Window - With In-Line Reveal - Single Glazed</t>
+          <t>Aluminium B SG Clear</t>
         </is>
       </c>
       <c r="H12" s="18" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
@@ -1658,47 +1454,47 @@
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
-          <t>NatHERS p.5, p.6</t>
+          <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>BED 4</t>
+          <t>Bedroom 1</t>
         </is>
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="C13" s="19" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>1450</v>
+        <v>500</v>
       </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>Awning</t>
+          <t>awning</t>
         </is>
       </c>
       <c r="F13" s="18" t="inlineStr">
         <is>
-          <t>NNW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>150 Series Thermal Star Aluminium Awning Window - With In-Line Reveal - Single Glazed</t>
+          <t>Aluminium A SG Clear</t>
         </is>
       </c>
       <c r="H13" s="18" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
@@ -1710,99 +1506,99 @@
       </c>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t>NatHERS p.5, p.6</t>
+          <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>KITCHEN/FAMILY/DINING</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="n">
-        <v>2100</v>
-      </c>
-      <c r="D14" s="22" t="n">
-        <v>2140</v>
-      </c>
-      <c r="E14" s="20" t="inlineStr">
-        <is>
-          <t>Sliding Door</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t>NNW</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
-        <is>
-          <t>A&amp;L Aluminium Sliding Door - Single Glazed - with In-Line Reveal</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I14" s="21" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="J14" s="20" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Bedroom 2</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium B SG Clear</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K14" s="22" t="n">
+      <c r="K14" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L14" s="20" t="inlineStr">
-        <is>
-          <t>NatHERS p.5, p.6</t>
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>LOUNGE</t>
+          <t>Kitchen/Living</t>
         </is>
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="C15" s="19" t="n">
-        <v>1800</v>
+        <v>1100</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>610</v>
+        <v>2400</v>
       </c>
       <c r="E15" s="17" t="inlineStr">
         <is>
-          <t>Awning</t>
+          <t>sliding</t>
         </is>
       </c>
       <c r="F15" s="18" t="inlineStr">
         <is>
-          <t>NNW</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>150 Series Thermal Star Aluminium Awning Window - With In-Line Reveal - Single Glazed</t>
+          <t>Aluminium B SG Clear</t>
         </is>
       </c>
       <c r="H15" s="18" t="n">
-        <v>4.1</v>
+        <v>6.7</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>0.53</v>
+        <v>0.7</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
@@ -1814,7 +1610,111 @@
       </c>
       <c r="L15" s="17" t="inlineStr">
         <is>
-          <t>NatHERS p.5, p.6</t>
+          <t>NatHERS p.6, p.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>LDRY</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>820</v>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>hinged door</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>Aluminium B SG Clear</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K16" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>NatHERS p.6, p.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>820</v>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>hinged door</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>Aluminium B SG Clear</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>

--- a/outputs/test_takeoff_output.xlsx
+++ b/outputs/test_takeoff_output.xlsx
@@ -71,7 +71,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -86,32 +86,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FEF9E7"/>
+        <bgColor rgb="00FEF9E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FDEDEC"/>
         <bgColor rgb="00FDEDEC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF9E7"/>
-        <bgColor rgb="00FEF9E7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDF7F2"/>
-        <bgColor rgb="00FDF7F2"/>
+        <fgColor rgb="00F2FDF8"/>
+        <bgColor rgb="00F2FDF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F7FD"/>
         <bgColor rgb="00F2F7FD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2FDF8"/>
-        <bgColor rgb="00F2FDF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -141,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,16 +150,16 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -186,15 +180,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -562,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -610,7 +595,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -620,7 +605,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -631,7 +616,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>76.8%</t>
         </is>
       </c>
     </row>
@@ -674,168 +659,185 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1118</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
+          <t>2136ALSD</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Dimension Mismatch</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for 1118 (Bedroom 3): Plans 1100H×1800W vs NatHERS 1100H×1810W.</t>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Dimension mismatch for 2136ALSD (Kitchen/Living): Plans 2130H×3600W vs NatHERS 2100H×3600W.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
+          <t>820d</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Dimension Mismatch</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for 1006 (ens): Plans 1000H×600W vs NatHERS 1800H×600W.</t>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Dimension mismatch for 820d (LDRY): Plans 2040H×820W vs NatHERS 2100H×820W.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>820d</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>Dimension Mismatch</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Dimension mismatch for 820d (ENTRY): Plans 2040H×820W vs NatHERS 2100H×820W.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>1117 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>Dimension Mismatch</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Dimension mismatch for 1118 (Bedroom 3): Plans 1100H×1800W vs NatHERS 1100H×1810W.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>Dimension Mismatch</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Dimension mismatch for 1006 (ens): Plans 1000H×600W vs NatHERS 1800H×600W.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1818</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Missing in Plans</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>1818 (Bedroom 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1124</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Missing in Plans</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>1124 (Kitchen/Living) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>1117 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Missing in Plans</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>D1 (LDRY) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Missing in Plans</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>D2 (ENTRY) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>1818 (Bedroom 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
+          <t>1124</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Missing in Plans</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>1124 (Kitchen/Living) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>BASIX Glazing Total</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>BASIX Area Mismatch</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Extracted plan glazing area (28.90 m²) differs from BASIX certificate total (36.90 m²) by 21.7%. The BASIX/NatHERS certificate value (36.90 m²) is the verified anchor. Review the plan extraction for under-counting — possible phantom openings, excluded door types, or scanned-page misreads.</t>
         </is>
@@ -852,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -991,269 +993,269 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>WIR</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>1806</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D4" s="19" t="n">
-        <v>600</v>
-      </c>
-      <c r="E4" s="17" t="inlineStr">
-        <is>
-          <t>fixed</t>
-        </is>
-      </c>
-      <c r="F4" s="18" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>LDRY</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>820d</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>820</v>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>hinged door</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>Aluminium B SG Clear</t>
         </is>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="H4" s="15" t="n">
         <v>6.7</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="I4" s="15" t="n">
         <v>0.7</v>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K4" s="19" t="n">
+      <c r="K4" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>Bedroom 3</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>1118</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="n">
-        <v>1100</v>
-      </c>
-      <c r="D5" s="19" t="n">
-        <v>1810</v>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>sliding</t>
-        </is>
-      </c>
-      <c r="F5" s="18" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>820d</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>820</v>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>hinged door</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>Aluminium B SG Clear</t>
         </is>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="15" t="n">
         <v>6.7</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="15" t="n">
         <v>0.7</v>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="K5" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="14" t="inlineStr">
         <is>
           <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>BATH</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>1115</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>1100</v>
-      </c>
-      <c r="D6" s="19" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>sliding</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium B SG Clear</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I6" s="18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium</t>
-        </is>
-      </c>
-      <c r="K6" s="19" t="n">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>BED 2</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>820d</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>820</v>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>hinged door</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Per NatHERS Schedule</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="17" t="inlineStr">
-        <is>
-          <t>Plans p.4 / NatHERS p.6, p.7</t>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>Plans p.4</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>ens</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>600</v>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>awning</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium A SG Clear</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I7" s="18" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium</t>
-        </is>
-      </c>
-      <c r="K7" s="19" t="n">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>BED 2</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>820d</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>820</v>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>hinged door</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Per NatHERS Schedule</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="n"/>
+      <c r="K7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="17" t="inlineStr">
-        <is>
-          <t>Plans p.4 / NatHERS p.6, p.7</t>
+      <c r="L7" s="14" t="inlineStr">
+        <is>
+          <t>Plans p.4</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>Kitchen/Living</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>1806</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D8" s="19" t="n">
-        <v>600</v>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>awning</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium A SG Clear</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I8" s="18" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium</t>
-        </is>
-      </c>
-      <c r="K8" s="19" t="n">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>BED 2</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>820d</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>820</v>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>hinged door</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Per NatHERS Schedule</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="n"/>
+      <c r="K8" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t>Plans p.4 / NatHERS p.6, p.7</t>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>Plans p.4</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>Kitchen/Living</t>
+          <t>WIR</t>
         </is>
       </c>
       <c r="B9" s="18" t="inlineStr">
@@ -1269,7 +1271,7 @@
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>awning</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="F9" s="18" t="inlineStr">
@@ -1279,14 +1281,14 @@
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>Aluminium A SG Clear</t>
+          <t>Aluminium B SG Clear</t>
         </is>
       </c>
       <c r="H9" s="18" t="n">
         <v>6.7</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
@@ -1305,40 +1307,40 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>Kitchen/Living</t>
+          <t>Bedroom 3</t>
         </is>
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="C10" s="19" t="n">
-        <v>1800</v>
+        <v>1100</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>600</v>
+        <v>1810</v>
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>awning</t>
+          <t>sliding</t>
         </is>
       </c>
       <c r="F10" s="18" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>Aluminium A SG Clear</t>
+          <t>Aluminium B SG Clear</t>
         </is>
       </c>
       <c r="H10" s="18" t="n">
         <v>6.7</v>
       </c>
       <c r="I10" s="18" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
@@ -1357,40 +1359,40 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>Bedroom 1</t>
+          <t>BATH</t>
         </is>
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="C11" s="19" t="n">
         <v>1100</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>awning</t>
+          <t>sliding</t>
         </is>
       </c>
       <c r="F11" s="18" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>Aluminium A SG Clear</t>
+          <t>Aluminium B SG Clear</t>
         </is>
       </c>
       <c r="H11" s="18" t="n">
         <v>6.7</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
@@ -1402,78 +1404,78 @@
       </c>
       <c r="L11" s="17" t="inlineStr">
         <is>
-          <t>NatHERS p.6, p.7</t>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>Bedroom 1</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="n">
-        <v>1100</v>
-      </c>
-      <c r="D12" s="19" t="n">
-        <v>1700</v>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>double_hung</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium B SG Clear</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium</t>
-        </is>
-      </c>
-      <c r="K12" s="19" t="n">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>820d</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>820</v>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>hinged door</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Per NatHERS Schedule</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="n"/>
+      <c r="K12" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t>NatHERS p.6, p.7</t>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>Plans p.4</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>Bedroom 1</t>
+          <t>ens</t>
         </is>
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="C13" s="19" t="n">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
@@ -1482,7 +1484,7 @@
       </c>
       <c r="F13" s="18" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
@@ -1506,47 +1508,47 @@
       </c>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t>NatHERS p.6, p.7</t>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>Bedroom 2</t>
+          <t>Kitchen/Living</t>
         </is>
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="C14" s="19" t="n">
         <v>1800</v>
       </c>
       <c r="D14" s="19" t="n">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>sliding</t>
+          <t>awning</t>
         </is>
       </c>
       <c r="F14" s="18" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>Aluminium B SG Clear</t>
+          <t>Aluminium A SG Clear</t>
         </is>
       </c>
       <c r="H14" s="18" t="n">
         <v>6.7</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
@@ -1558,7 +1560,7 @@
       </c>
       <c r="L14" s="17" t="inlineStr">
         <is>
-          <t>NatHERS p.6, p.7</t>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1570,35 +1572,35 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="C15" s="19" t="n">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>2400</v>
+        <v>600</v>
       </c>
       <c r="E15" s="17" t="inlineStr">
         <is>
-          <t>sliding</t>
+          <t>awning</t>
         </is>
       </c>
       <c r="F15" s="18" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>Aluminium B SG Clear</t>
+          <t>Aluminium A SG Clear</t>
         </is>
       </c>
       <c r="H15" s="18" t="n">
         <v>6.7</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
@@ -1610,109 +1612,317 @@
       </c>
       <c r="L15" s="17" t="inlineStr">
         <is>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Kitchen/Living</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>awning</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium A SG Clear</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="17" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Bedroom 1</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>awning</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium A SG Clear</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J17" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="17" t="inlineStr">
+        <is>
           <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>LDRY</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="n">
-        <v>2100</v>
-      </c>
-      <c r="D16" s="22" t="n">
-        <v>820</v>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>hinged door</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Bedroom 1</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>double_hung</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>Aluminium B SG Clear</t>
         </is>
       </c>
-      <c r="H16" s="21" t="n">
+      <c r="H18" s="18" t="n">
         <v>6.7</v>
       </c>
-      <c r="I16" s="21" t="n">
+      <c r="I18" s="18" t="n">
         <v>0.7</v>
       </c>
-      <c r="J16" s="20" t="inlineStr">
+      <c r="J18" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K16" s="22" t="n">
+      <c r="K18" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L16" s="20" t="inlineStr">
+      <c r="L18" s="17" t="inlineStr">
         <is>
           <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="n">
-        <v>2100</v>
-      </c>
-      <c r="D17" s="22" t="n">
-        <v>820</v>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>hinged door</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Bedroom 1</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>awning</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium A SG Clear</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J19" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K19" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="17" t="inlineStr">
+        <is>
+          <t>NatHERS p.6, p.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Bedroom 2</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>Aluminium B SG Clear</t>
         </is>
       </c>
-      <c r="H17" s="21" t="n">
+      <c r="H20" s="18" t="n">
         <v>6.7</v>
       </c>
-      <c r="I17" s="21" t="n">
+      <c r="I20" s="18" t="n">
         <v>0.7</v>
       </c>
-      <c r="J17" s="20" t="inlineStr">
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K17" s="22" t="n">
+      <c r="K20" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L17" s="20" t="inlineStr">
+      <c r="L20" s="17" t="inlineStr">
+        <is>
+          <t>NatHERS p.6, p.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Kitchen/Living</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>1124</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium B SG Clear</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I21" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J21" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="17" t="inlineStr">
         <is>
           <t>NatHERS p.6, p.7</t>
         </is>

--- a/outputs/test_takeoff_output.xlsx
+++ b/outputs/test_takeoff_output.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -616,7 +616,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>74.0%</t>
         </is>
       </c>
     </row>
@@ -667,16 +667,16 @@
           <t>Dimension Mismatch</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for 2136ALSD (Kitchen/Living): Plans 2130H×3600W vs NatHERS 2100H×3600W.</t>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Dimension mismatch for 2136ALSD (Kitchen/Living): Plans 2130H×3600W vs NatHERS 2100H×3600W (Difference: 30mm).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>820d</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -684,16 +684,16 @@
           <t>Dimension Mismatch</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for 820d (LDRY): Plans 2040H×820W vs NatHERS 2100H×820W.</t>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Dimension mismatch for 1118 (Bedroom 3): Plans 1100H×1800W vs NatHERS 1100H×1810W (Difference: 10mm).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>820d</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -703,41 +703,41 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Dimension mismatch for 820d (ENTRY): Plans 2040H×820W vs NatHERS 2100H×820W.</t>
+          <t>Dimension mismatch for 1006 (ens): Plans 1000H×600W vs NatHERS 1800H×600W (Difference: 800mm).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1118</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Dimension Mismatch</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for 1118 (Bedroom 3): Plans 1100H×1800W vs NatHERS 1100H×1810W.</t>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Missing in Plans</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Dimension Mismatch</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Dimension mismatch for 1006 (ens): Plans 1000H×600W vs NatHERS 1800H×600W.</t>
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Missing in Plans</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>1117 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>1117 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>1818 (Bedroom 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
@@ -788,58 +788,24 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>1105 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>1124 (Kitchen/Living) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1818</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>1818 (Bedroom 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>1124</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>1124 (Kitchen/Living) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
           <t>BASIX Glazing Total</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>BASIX Area Mismatch</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Extracted plan glazing area (28.90 m²) differs from BASIX certificate total (36.90 m²) by 21.7%. The BASIX/NatHERS certificate value (36.90 m²) is the verified anchor. Review the plan extraction for under-counting — possible phantom openings, excluded door types, or scanned-page misreads.</t>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Extracted plan glazing area (25.45 m²) differs from BASIX certificate total (36.90 m²) by 31.0%. The BASIX/NatHERS certificate value (36.90 m²) is the verified anchor. Review the plan extraction for under-counting — possible phantom openings, excluded door types, or scanned-page misreads.</t>
         </is>
       </c>
     </row>
@@ -854,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -993,269 +959,269 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>LDRY</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>820d</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="n">
-        <v>2100</v>
-      </c>
-      <c r="D4" s="16" t="n">
-        <v>820</v>
-      </c>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
-          <t>hinged door</t>
-        </is>
-      </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>WIR</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D4" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium B SG Clear</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Bedroom 3</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>1118</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>1810</v>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium B SG Clear</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="17" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>BATH</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>Aluminium B SG Clear</t>
         </is>
       </c>
-      <c r="H4" s="15" t="n">
+      <c r="H6" s="18" t="n">
         <v>6.7</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I6" s="18" t="n">
         <v>0.7</v>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K4" s="16" t="n">
+      <c r="K6" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>820d</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>2100</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>820</v>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>hinged door</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Aluminium B SG Clear</t>
-        </is>
-      </c>
-      <c r="H5" s="15" t="n">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>ens</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>awning</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium A SG Clear</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="n">
         <v>6.7</v>
       </c>
-      <c r="I5" s="15" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="I7" s="18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K5" s="16" t="n">
+      <c r="K7" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="14" t="inlineStr">
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>BED 2</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>820d</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>2040</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>820</v>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>hinged door</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>Per NatHERS Schedule</t>
-        </is>
-      </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="14" t="n"/>
-      <c r="K6" s="16" t="n">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Kitchen/Living</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>awning</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium A SG Clear</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K8" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="14" t="inlineStr">
-        <is>
-          <t>Plans p.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>BED 2</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>820d</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>2040</v>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>820</v>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>hinged door</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Per NatHERS Schedule</t>
-        </is>
-      </c>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="14" t="n"/>
-      <c r="K7" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="14" t="inlineStr">
-        <is>
-          <t>Plans p.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>BED 2</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>820d</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="n">
-        <v>2040</v>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>820</v>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>hinged door</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>Per NatHERS Schedule</t>
-        </is>
-      </c>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="14" t="n"/>
-      <c r="K8" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
-        <is>
-          <t>Plans p.4</t>
+      <c r="L8" s="17" t="inlineStr">
+        <is>
+          <t>Plans p.4 / NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>WIR</t>
+          <t>Kitchen/Living</t>
         </is>
       </c>
       <c r="B9" s="18" t="inlineStr">
@@ -1271,7 +1237,7 @@
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>awning</t>
         </is>
       </c>
       <c r="F9" s="18" t="inlineStr">
@@ -1281,14 +1247,14 @@
       </c>
       <c r="G9" s="17" t="inlineStr">
         <is>
-          <t>Aluminium B SG Clear</t>
+          <t>Aluminium A SG Clear</t>
         </is>
       </c>
       <c r="H9" s="18" t="n">
         <v>6.7</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
@@ -1307,40 +1273,40 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>Bedroom 3</t>
+          <t>Kitchen/Living</t>
         </is>
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="C10" s="19" t="n">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>1810</v>
+        <v>600</v>
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>sliding</t>
+          <t>awning</t>
         </is>
       </c>
       <c r="F10" s="18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>Aluminium B SG Clear</t>
+          <t>Aluminium A SG Clear</t>
         </is>
       </c>
       <c r="H10" s="18" t="n">
         <v>6.7</v>
       </c>
       <c r="I10" s="18" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
@@ -1359,40 +1325,40 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>BATH</t>
+          <t>Bedroom 1</t>
         </is>
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="C11" s="19" t="n">
         <v>1100</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>sliding</t>
+          <t>awning</t>
         </is>
       </c>
       <c r="F11" s="18" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>SW</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>Aluminium B SG Clear</t>
+          <t>Aluminium A SG Clear</t>
         </is>
       </c>
       <c r="H11" s="18" t="n">
         <v>6.7</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
@@ -1404,78 +1370,78 @@
       </c>
       <c r="L11" s="17" t="inlineStr">
         <is>
-          <t>Plans p.4 / NatHERS p.6, p.7</t>
+          <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>820d</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>2040</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>820</v>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>hinged door</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>Per NatHERS Schedule</t>
-        </is>
-      </c>
-      <c r="H12" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="n"/>
-      <c r="K12" s="16" t="n">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Bedroom 1</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>double_hung</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium B SG Clear</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="K12" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L12" s="14" t="inlineStr">
-        <is>
-          <t>Plans p.4</t>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>ens</t>
+          <t>Bedroom 1</t>
         </is>
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="C13" s="19" t="n">
-        <v>1800</v>
+        <v>1100</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
@@ -1484,7 +1450,7 @@
       </c>
       <c r="F13" s="18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
@@ -1508,47 +1474,47 @@
       </c>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t>Plans p.4 / NatHERS p.6, p.7</t>
+          <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>Kitchen/Living</t>
+          <t>Bedroom 2</t>
         </is>
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="C14" s="19" t="n">
         <v>1800</v>
       </c>
       <c r="D14" s="19" t="n">
-        <v>600</v>
+        <v>1800</v>
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>awning</t>
+          <t>sliding</t>
         </is>
       </c>
       <c r="F14" s="18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>Aluminium A SG Clear</t>
+          <t>Aluminium B SG Clear</t>
         </is>
       </c>
       <c r="H14" s="18" t="n">
         <v>6.7</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
@@ -1560,7 +1526,7 @@
       </c>
       <c r="L14" s="17" t="inlineStr">
         <is>
-          <t>Plans p.4 / NatHERS p.6, p.7</t>
+          <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1572,35 +1538,35 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="C15" s="19" t="n">
-        <v>1800</v>
+        <v>1100</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>600</v>
+        <v>2400</v>
       </c>
       <c r="E15" s="17" t="inlineStr">
         <is>
-          <t>awning</t>
+          <t>sliding</t>
         </is>
       </c>
       <c r="F15" s="18" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
         <is>
-          <t>Aluminium A SG Clear</t>
+          <t>Aluminium B SG Clear</t>
         </is>
       </c>
       <c r="H15" s="18" t="n">
         <v>6.7</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>0.57</v>
+        <v>0.7</v>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
@@ -1612,317 +1578,101 @@
       </c>
       <c r="L15" s="17" t="inlineStr">
         <is>
-          <t>Plans p.4 / NatHERS p.6, p.7</t>
+          <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>Kitchen/Living</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>1806</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D16" s="19" t="n">
-        <v>600</v>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>awning</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>LDRY</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>820</v>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>hinged door</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium A SG Clear</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium</t>
-        </is>
-      </c>
-      <c r="K16" s="19" t="n">
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="n"/>
+      <c r="K16" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>Plans p.4 / NatHERS p.6, p.7</t>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>NatHERS p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>Bedroom 1</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>1105</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="n">
-        <v>1100</v>
-      </c>
-      <c r="D17" s="19" t="n">
-        <v>500</v>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>awning</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>SW</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium A SG Clear</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium</t>
-        </is>
-      </c>
-      <c r="K17" s="19" t="n">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>820</v>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>hinged door</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>NatHERS p.6, p.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Bedroom 1</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="n">
-        <v>1100</v>
-      </c>
-      <c r="D18" s="19" t="n">
-        <v>1700</v>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>double_hung</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium B SG Clear</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium</t>
-        </is>
-      </c>
-      <c r="K18" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="17" t="inlineStr">
-        <is>
-          <t>NatHERS p.6, p.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Bedroom 1</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>1105</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="n">
-        <v>1100</v>
-      </c>
-      <c r="D19" s="19" t="n">
-        <v>500</v>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>awning</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium A SG Clear</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I19" s="18" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium</t>
-        </is>
-      </c>
-      <c r="K19" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" s="17" t="inlineStr">
-        <is>
-          <t>NatHERS p.6, p.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Bedroom 2</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D20" s="19" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>sliding</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium B SG Clear</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I20" s="18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium</t>
-        </is>
-      </c>
-      <c r="K20" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="17" t="inlineStr">
-        <is>
-          <t>NatHERS p.6, p.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>Kitchen/Living</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>1124</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="n">
-        <v>1100</v>
-      </c>
-      <c r="D21" s="19" t="n">
-        <v>2400</v>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>sliding</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium B SG Clear</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J21" s="17" t="inlineStr">
-        <is>
-          <t>Aluminium</t>
-        </is>
-      </c>
-      <c r="K21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" s="17" t="inlineStr">
+      <c r="L17" s="14" t="inlineStr">
         <is>
           <t>NatHERS p.6, p.7</t>
         </is>
